--- a/textos/capitulos/9_plano_financeiro_modelo.xlsx
+++ b/textos/capitulos/9_plano_financeiro_modelo.xlsx
@@ -911,7 +911,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Noite de sexta e sábado: 26.9% a 60.3% (média 41.7%). O dia inteiro fica abaixo do pico da noite.</t>
+          <t>Noite de sexta e sábado: 29.9% a 66.9% (média 46.1%). O dia inteiro fica abaixo do pico da noite.</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">

--- a/textos/capitulos/9_plano_financeiro_modelo.xlsx
+++ b/textos/capitulos/9_plano_financeiro_modelo.xlsx
@@ -4068,11 +4068,11 @@
         <v/>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18.75</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Mediana do couvert ou taxa de jogo nos cardápios de 8 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
+          <t>Mediana do couvert ou taxa de jogo nos cardápios de 13 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
         </is>
       </c>
     </row>

--- a/textos/capitulos/9_plano_financeiro_modelo.xlsx
+++ b/textos/capitulos/9_plano_financeiro_modelo.xlsx
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Mediana do couvert ou taxa de jogo nos cardápios de 13 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
+          <t>Mediana do couvert ou taxa de jogo nos cardápios de 21 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
         </is>
       </c>
     </row>

--- a/textos/capitulos/9_plano_financeiro_modelo.xlsx
+++ b/textos/capitulos/9_plano_financeiro_modelo.xlsx
@@ -4072,7 +4072,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Mediana do couvert ou taxa de jogo nos cardápios de 21 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
+          <t>Mediana do couvert ou taxa de jogo nos cardápios de 22 concorrentes (B1); acima dela, o posicionamento tem de justificar</t>
         </is>
       </c>
     </row>
